--- a/帝国时代2决定版 文明联盟 象兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 象兵流最优研究顺序 By RemonBo.xlsx
@@ -18,15 +18,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·象兵本体强化'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·象兵本体强化'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·象兵本体强化'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与象兵流无关·可跳过'!$A$1:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与象兵流无关·可跳过'!$A$1:$D$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与象兵流无关·可跳过'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'全62文明总名次'!$A$1:$F$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'全62文明总名次'!$1:$1</definedName>
@@ -576,11 +576,11 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 13/16；缺 Ballista Elephant、Elite Ballista Elephant、Chatras；最直接一条：象兵额外受伤-25%且抗招降</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -590,11 +590,11 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
+          <t>备选：原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：宝伞（象兵生命+100）</t>
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；象兵科技树 11/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>原生条目 3 条（强 3 / 弱 0）；象兵科技树 11/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵移速+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -646,11 +646,11 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵城堡/帝王费用-25/35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 Battle Elephant、Elite Battle Elephant、Ballista Elephant、Elite Ballista Elephant；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>备选：原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="51" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>第 3 位</t>
@@ -688,15 +688,23 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 Elite Battle Elephant、Ballista Elephant、Elite Ballista Elephant、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>契丹（备选）</t>
+        </is>
+      </c>
       <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
@@ -722,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -765,7 +773,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>4</v>
       </c>
@@ -791,11 +799,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
@@ -821,11 +829,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
+          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
@@ -851,7 +859,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵城堡/帝王费用-25/35%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
     </row>
@@ -881,12 +889,42 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 Battle Elephant、Elite Battle Elephant、Ballista Elephant、Elite Ballista Elephant；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -898,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1259,8 +1297,35 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>战斗中持续回血：攻速越快回得越多，是唯一的骑兵续航引擎，缠斗越久优势越大</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1349,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1999,12 +2064,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2014,19 +2079,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧场取代农田」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2036,19 +2101,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>骆驼和海军文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2058,19 +2123,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>骆驼和海军文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2080,19 +2145,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2102,19 +2167,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2124,19 +2189,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2146,19 +2211,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2168,19 +2233,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2190,19 +2255,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2212,19 +2277,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2234,19 +2299,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2256,19 +2321,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2278,19 +2343,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2300,19 +2365,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2322,19 +2387,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2344,19 +2409,19 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2366,19 +2431,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2388,19 +2453,19 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2410,19 +2475,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2432,19 +2497,19 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2454,19 +2519,19 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2476,19 +2541,19 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2498,19 +2563,19 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「高地受伤-10%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2520,14 +2585,14 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2542,19 +2607,19 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2564,34 +2629,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D56"/>
+  <autoFilter ref="A1:D55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2603,7 +2646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2661,7 +2704,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 13/16。缺：Ballista Elephant、Elite Ballista Elephant、Chatras</t>
+          <t>原生条目 2 条（强 2）；象兵科技树 13/16。缺：重弩战象、精锐重弩战象、宝伞</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2729,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3）；象兵科技树 11/16。缺：Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant、Chatras</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 11/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、宝伞</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2754,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：Elite Battle Elephant、Ballista Elephant、Elite Ballista Elephant、血统、骑兵板甲</t>
+          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：精锐战斗象、重弩战象、精锐重弩战象、血统、骑兵板甲</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2779,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 9/16。缺：Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant、Ballista Elephant</t>
+          <t>原生条目 2 条（强 2）；象兵科技树 9/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2804,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；象兵科技树 9/16。缺：Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant、Ballista Elephant</t>
+          <t>原生条目 1 条（强 1）；象兵科技树 9/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2829,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；象兵科技树 6/16。缺：Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant、Ballista Elephant</t>
+          <t>原生条目 1 条（强 1）；象兵科技树 6/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2854,37 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：Battle Elephant、Elite Battle Elephant、Ballista Elephant、Elite Ballista Elephant、高炉</t>
+          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：战斗象、精锐战斗象、重弩战象、精锐重弩战象、高炉</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 1）；象兵科技树 5/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2871,7 +2939,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -2897,11 +2965,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 13/16；缺 Ballista Elephant、Elite Ballista Elephant、Chatras；最直接一条：象兵额外受伤-25%且抗招降</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -2927,11 +2995,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；象兵科技树 11/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
+          <t>原生条目 3 条（强 3 / 弱 0）；象兵科技树 11/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵移速+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -2957,11 +3025,11 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 Elite Battle Elephant、Ballista Elephant、Elite Ballista Elephant、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -2987,11 +3055,11 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -3017,11 +3085,11 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -3047,7 +3115,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 Elephant Archer、Elite Elephant Archer、Armored Elephant、Siege Elephant；最直接一条：象兵城堡/帝王费用-25/35%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3145,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 Battle Elephant、Elite Battle Elephant、Ballista Elephant、Elite Ballista Elephant；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -3087,27 +3155,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3185,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -3137,7 +3205,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3215,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3167,7 +3235,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3245,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3197,7 +3265,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3275,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3227,7 +3295,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3305,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -3257,7 +3325,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3335,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -3287,7 +3355,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3365,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -3317,7 +3385,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3395,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -3347,7 +3415,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3425,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -3377,7 +3445,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3455,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3407,7 +3475,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3485,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -3437,7 +3505,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3515,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3467,7 +3535,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3545,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -3497,7 +3565,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3575,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -3527,7 +3595,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3605,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -3557,7 +3625,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3635,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -3587,7 +3655,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3665,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -3617,7 +3685,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3695,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3647,7 +3715,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3725,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3677,7 +3745,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3755,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3707,7 +3775,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3785,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -3737,7 +3805,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3815,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -3767,7 +3835,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3845,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -3797,7 +3865,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3875,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -3827,7 +3895,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3905,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -3857,7 +3925,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3935,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -3887,7 +3955,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3965,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -3917,7 +3985,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3995,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -3947,7 +4015,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧场取代农田」）</t>
+          <t>海军和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工产食+木材」）</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4823,111 +4891,115 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>全表只有 6 个文明能造战象（孟加拉/高棉/达罗毗荼/缅甸/越南/马来），另有 1 个（瞿折罗）能出骑象弓兵——主选文明必须先解决「能不能出象」，再谈按钮加成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="10" t="inlineStr"/>
-      <c r="B9" s="10" t="inlineStr"/>
+          <t>全表共 10 个文明拥有象兵系单位（孟加拉/高棉/达罗毗荼/缅甸/越南/马来/瞿折罗/波斯/印度斯坦/普鲁人），但只有前 7 家带象兵专属加成——主选文明必须先解决「能不能出象」，再谈按钮加成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>决定性前提 4</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>契丹的「斡鲁朵骑兵」对战斗象/装甲象/战象生效（它们同属骑兵类），对骑象弓兵不生效——但契丹自己造不出象兵，它出现在本表是作为「按钮选项」：底座文明能出象时，再买契丹按钮即可让象兵战斗中回血。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>模组专属：按钮机制</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
-        </is>
-      </c>
+      <c r="A10" s="10" t="inlineStr"/>
+      <c r="B10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>模组专属：无专属机制</t>
+          <t>模组专属：按钮机制</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>已确认模组文本（v21）中没有任何针对象兵的独立按钮或 SSR 互斥项。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1">
+          <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="49" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
+          <t>模组专属：契丹「斡鲁朵骑兵」对象兵有效</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>该效果的真实实现是给 dat class 12（骑兵）与 class 47（斥候）统一加「战斗中回血」，再逐个剔除名单外的单位。战斗象、装甲象、老式战象（以及印度的 ELEITIS）类别都是 12，因此都能战斗中回血；骑象弓兵（class 36）不生效，重弩战象被官方显式排除。所以「象兵流 + 契丹按钮」是可行的组合，但别指望骑象弓兵也回血。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>模组专属：无象兵 SSR</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>除上述外，模组文本（v21）中没有针对象兵的独立按钮或 SSR 互斥项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
           <t>排序口径</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>① 只看直接作用于象兵本体、或其前置/费用/产出的条目；</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="10" t="inlineStr"/>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与象兵流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="10" t="inlineStr"/>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>② 泛用条目与兵种类一律剔除（放进「与象兵流无关·可跳过」）；</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr"/>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="10" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>未验证项</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="10" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>★ 最重要的一条：别买重复</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
@@ -4935,29 +5007,49 @@
       <c r="A20" s="10" t="inlineStr"/>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="10" t="inlineStr"/>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 象兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 象兵流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·象兵本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与象兵流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,15 +18,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·象兵本体强化'!$A$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·象兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与象兵流无关·可跳过'!$A$1:$D$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与象兵流无关·可跳过'!$A$1:$D$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与象兵流无关·可跳过'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'全62文明总名次'!$A$1:$F$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'全62文明总名次'!$1:$1</definedName>
@@ -73,7 +73,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +88,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE9CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,10 +152,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -576,7 +584,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
         </is>
       </c>
     </row>
@@ -590,7 +598,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -604,7 +612,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
         </is>
       </c>
     </row>
@@ -632,35 +640,35 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；象兵科技树 11/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 11/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵移速+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>马来（备选）</t>
+          <t>瞿折罗（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗（备选）</t>
+          <t>契丹（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
     </row>
@@ -688,7 +696,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -696,21 +704,29 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>契丹（备选）</t>
+          <t>马来（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>备选：阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔（备选）</t>
+        </is>
+      </c>
       <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>备选：阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="inlineStr"/>
@@ -730,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -773,7 +789,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>4</v>
       </c>
@@ -799,7 +815,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -829,17 +845,17 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -849,17 +865,17 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -869,7 +885,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -879,7 +895,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -889,17 +905,17 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -909,22 +925,202 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>城堡时代起</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>马厩单位城堡/帝王费用-15/20%</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代起</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>斥候系费用-15%</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>无条件</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 2 条（强 0 / 弱 2）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代起</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 2/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -974,7 +1170,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1001,7 +1197,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1028,7 +1224,7 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1055,7 +1251,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1082,7 +1278,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1109,7 +1305,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1136,7 +1332,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1337,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1401,8 +1597,197 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>马厩单位城堡/帝王费用-15/20%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>斥候系费用-15%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>血统/斥候食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>贵族特权（骑士黄金费用-60%）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1414,7 +1799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1492,12 +1877,12 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>防御文明</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1507,19 +1892,19 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>防御文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1529,19 +1914,19 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1551,19 +1936,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1573,14 +1958,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1595,19 +1980,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步弓手文明</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1617,19 +2002,19 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1639,19 +2024,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>步弓手文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1661,19 +2046,19 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1683,19 +2068,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>防御和海军文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1705,19 +2090,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1727,19 +2112,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>防御和海军文明</t>
+          <t>防御和骑兵文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1749,19 +2134,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和攻城武器文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1771,19 +2156,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>防御和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1793,19 +2178,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明</t>
+          <t>骑兵和僧侣文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1815,19 +2200,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1837,19 +2222,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1859,19 +2244,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1881,19 +2266,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1903,19 +2288,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明</t>
+          <t>弓兵与僧侣文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1925,19 +2310,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑兵和火药文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1947,19 +2332,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1969,19 +2354,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1991,19 +2376,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明</t>
+          <t>骆驼和海军文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2013,19 +2398,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2035,19 +2420,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2057,19 +2442,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2079,19 +2464,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2101,19 +2486,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>骆驼和海军文明</t>
+          <t>骑兵和海军文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2123,19 +2508,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2145,19 +2530,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2167,19 +2552,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2189,19 +2574,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2211,19 +2596,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>火药文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2233,19 +2618,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2255,14 +2640,14 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2277,19 +2662,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2299,19 +2684,19 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2321,19 +2706,19 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2343,19 +2728,19 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2365,19 +2750,19 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>弓兵和骑兵文明</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2387,19 +2772,19 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「造船厂工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2409,19 +2794,19 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「高地受伤-10%」）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>弓兵和象兵文明</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2431,19 +2816,19 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>骆驼和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2453,14 +2838,14 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2475,19 +2860,19 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2497,144 +2882,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>阿契美尼德</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>弓兵和骑兵文明</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「造船厂工作速度+15%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>步兵和骑兵文明</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「高地受伤-10%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>弓兵和象兵文明</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>步兵文明</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>步兵文明</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D55"/>
+  <autoFilter ref="A1:D49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2646,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2814,22 +3067,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>10/16</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；象兵科技树 6/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
+          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：战斗象、精锐战斗象、重弩战象、精锐重弩战象、高炉</t>
         </is>
       </c>
     </row>
@@ -2839,22 +3092,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>5/16</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：战斗象、精锐战斗象、重弩战象、精锐重弩战象、高炉</t>
+          <t>原生条目 1 条（强 1）；象兵科技树 5/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -2864,27 +3117,177 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；象兵科技树 5/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 1 条（强 1）；象兵科技树 6/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7/16</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>马厩单位城堡/帝王费用-15/20%</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7/16</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>斥候系费用-15%</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7/16</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7/16</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 2 条（强 0）；象兵科技树 6/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2/16</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 0）；象兵科技树 2/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2948,7 +3351,7 @@
           <t>孟加拉</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -2958,14 +3361,14 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
         </is>
       </c>
     </row>
@@ -2978,7 +3381,7 @@
           <t>高棉</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -2988,18 +3391,18 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>象兵移速+10%；獠牙剑（象兵攻击+3）；双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 3 / 弱 0）；象兵科技树 11/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵移速+10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 11/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵移速+10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -3008,7 +3411,7 @@
           <t>达罗毗荼</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3018,18 +3421,18 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>掷矛手/骑象弓兵攻速+25%；医疗部队（象兵每分钟恢复30生命）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -3048,14 +3451,14 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -3078,24 +3481,24 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>宝伞（象兵生命+100）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3108,14 +3511,14 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3528,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3138,24 +3541,24 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3168,14 +3571,14 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
     </row>
@@ -3185,27 +3588,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>马厩单位城堡/帝王费用-15/20%</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -3215,27 +3618,27 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
+          <t>2000 金</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>斥候系费用-15%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -3245,27 +3648,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗移速+5%，封建起+10%」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -3275,27 +3678,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -3305,27 +3708,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 0 / 弱 2）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -3335,27 +3738,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 2/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -3365,10 +3768,10 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3385,7 +3788,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -3395,10 +3798,10 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3415,7 +3818,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3425,10 +3828,10 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3445,7 +3848,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -3455,10 +3858,10 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3475,7 +3878,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
         </is>
       </c>
     </row>
@@ -3485,10 +3888,10 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3505,7 +3908,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
@@ -3515,10 +3918,10 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3535,7 +3938,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -3545,10 +3948,10 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3565,7 +3968,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -3575,10 +3978,10 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3595,7 +3998,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -3605,10 +4008,10 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3625,7 +4028,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -3635,10 +4038,10 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3655,7 +4058,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -3665,10 +4068,10 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3685,7 +4088,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3695,10 +4098,10 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3715,7 +4118,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -3725,10 +4128,10 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3745,7 +4148,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -3755,10 +4158,10 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3775,7 +4178,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
         </is>
       </c>
     </row>
@@ -3785,10 +4188,10 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3805,7 +4208,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -3815,10 +4218,10 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3835,7 +4238,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工存食+25%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
         </is>
       </c>
     </row>
@@ -3845,10 +4248,10 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3865,7 +4268,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民一击杀狼」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -3875,10 +4278,10 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3895,7 +4298,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -3905,10 +4308,10 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3925,7 +4328,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
         </is>
       </c>
     </row>
@@ -3935,10 +4338,10 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3955,7 +4358,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -3965,10 +4368,10 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -3985,7 +4388,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -3995,10 +4398,10 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4015,7 +4418,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -4025,10 +4428,10 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4045,7 +4448,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4458,10 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4075,7 +4478,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
@@ -4085,10 +4488,10 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4105,7 +4508,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
@@ -4115,10 +4518,10 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4135,7 +4538,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
@@ -4145,10 +4548,10 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4165,7 +4568,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
@@ -4175,10 +4578,10 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4195,7 +4598,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4205,10 +4608,10 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4225,7 +4628,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
         </is>
       </c>
     </row>
@@ -4235,10 +4638,10 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4255,7 +4658,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「金矿工速度+25%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4671,7 @@
           <t>瓦兰吉人</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4298,7 +4701,7 @@
           <t>维京</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4328,7 +4731,7 @@
           <t>魏</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4358,7 +4761,7 @@
           <t>吴</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4388,7 +4791,7 @@
           <t>西班牙</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4418,7 +4821,7 @@
           <t>西西里</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4448,7 +4851,7 @@
           <t>匈奴</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4478,7 +4881,7 @@
           <t>亚美尼亚</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4508,7 +4911,7 @@
           <t>意大利</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4538,7 +4941,7 @@
           <t>印度斯坦</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4568,7 +4971,7 @@
           <t>印加</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4598,7 +5001,7 @@
           <t>中国</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4628,7 +5031,7 @@
           <t>阿契美尼德</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4658,7 +5061,7 @@
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4688,7 +5091,7 @@
           <t>普鲁人</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4718,7 +5121,7 @@
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4748,7 +5151,7 @@
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4778,7 +5181,7 @@
           <t>雅典</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4812,7 +5215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4820,236 +5223,276 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>《帝国时代2 决定版》象兵流最优研究顺序</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>By RemonBo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="11" t="inlineStr"/>
-      <c r="B2" s="10" t="inlineStr"/>
+      <c r="A2" s="12" t="inlineStr"/>
+      <c r="B2" s="11" t="inlineStr"/>
     </row>
     <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>口径</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>62 个按钮 = 各文明的全部特性（主要功能 + 独特科技 + 团队加成），不含独特单位。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="10" t="inlineStr"/>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr"/>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>团队加成按「对自己生效」计算，不因原本是全队加成而降权。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="10" t="inlineStr"/>
-      <c r="B5" s="10" t="inlineStr"/>
+      <c r="A5" s="11" t="inlineStr"/>
+      <c r="B5" s="11" t="inlineStr"/>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>决定性前提 1</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>象兵出自马厩（城堡时代解锁），造价极高（食物 + 黄金），是典型的「一波定胜负」兵种。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>决定性前提 2</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>象兵生命极高但移速慢、怕长矛兵系与僧侣招降；象轿/宝伞/獠牙剑类专有科技决定其上限。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>决定性前提 3</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>全表共 10 个文明拥有象兵系单位（孟加拉/高棉/达罗毗荼/缅甸/越南/马来/瞿折罗/波斯/印度斯坦/普鲁人），但只有前 7 家带象兵专属加成——主选文明必须先解决「能不能出象」，再谈按钮加成。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>决定性前提 4</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>契丹的「斡鲁朵骑兵」对战斗象/装甲象/战象生效（它们同属骑兵类），对骑象弓兵不生效——但契丹自己造不出象兵，它出现在本表是作为「按钮选项」：底座文明能出象时，再买契丹按钮即可让象兵战斗中回血。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="10" t="inlineStr"/>
-      <c r="B10" s="10" t="inlineStr"/>
+      <c r="A10" s="11" t="inlineStr"/>
+      <c r="B10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>模组专属：按钮机制</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="49" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>模组专属：契丹「斡鲁朵骑兵」对象兵有效</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>该效果的真实实现是给 dat class 12（骑兵）与 class 47（斥候）统一加「战斗中回血」，再逐个剔除名单外的单位。战斗象、装甲象、老式战象（以及印度的 ELEITIS）类别都是 12，因此都能战斗中回血；骑象弓兵（class 36）不生效，重弩战象被官方显式排除。所以「象兵流 + 契丹按钮」是可行的组合，但别指望骑象弓兵也回血。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>模组专属：无象兵 SSR</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>除上述外，模组文本（v21）中没有针对象兵的独立按钮或 SSR 互斥项。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>排序口径</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>① 只看直接作用于象兵本体、或其前置/费用/产出的条目；</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与象兵流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="10" t="inlineStr"/>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>直接加强象兵本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>降低该兵种及同系兵种（骑兵系／马厩单位（象兵属骑兵类））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="10" t="inlineStr"/>
-      <c r="B17" s="10" t="inlineStr"/>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>④ 阶段 4 · 其他相关</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="11" t="inlineStr"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与象兵流无关·可跳过」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="11" t="inlineStr"/>
+      <c r="B20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>未验证项</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>★ 最重要的一条：别买重复</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="10" t="inlineStr"/>
-      <c r="B20" s="10" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>数据来源</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="10" t="inlineStr"/>
-      <c r="B22" s="10" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="11" t="inlineStr"/>
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 象兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 象兵流最优研究顺序 By RemonBo.xlsx
@@ -18,15 +18,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·象兵本体强化'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·象兵本体强化'!$A$1:$E$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·象兵本体强化'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与象兵流无关·可跳过'!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与象兵流无关·可跳过'!$A$1:$D$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与象兵流无关·可跳过'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'全62文明总名次'!$A$1:$F$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'全62文明总名次'!$1:$1</definedName>
@@ -73,7 +73,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +93,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF7CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -155,10 +160,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,12 +587,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）；骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：骑兵对掷矛手攻+2</t>
         </is>
       </c>
     </row>
@@ -598,7 +606,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -654,21 +662,21 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 7 条（强 3 / 弱 1）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>契丹（备选）</t>
+          <t>保加利亚（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：马镫（骑兵攻速+33%）</t>
         </is>
       </c>
     </row>
@@ -678,7 +686,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>第 3 位</t>
@@ -691,12 +699,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>掷矛手/骑象弓兵攻速+25%；医疗部队（象兵每分钟恢复30生命）</t>
+          <t>掷矛手/骑象弓兵攻速+25%；医疗部队（象兵每分钟恢复30生命）；乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -704,27 +712,27 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>马来（备选）</t>
+          <t>法兰克（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：骑兵封建起生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔（备选）</t>
+          <t>契丹（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
     </row>
@@ -746,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -805,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）；曼尼普尔马（骑兵对远程攻+4）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -865,17 +873,17 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 1）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
     </row>
@@ -885,7 +893,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -895,7 +903,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>马镫（骑兵攻速+33%）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -905,7 +913,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：马镫（骑兵攻速+33%）</t>
         </is>
       </c>
     </row>
@@ -915,7 +923,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -925,27 +933,27 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>骑兵封建起生命+20%；骑士精神（马厩工作速度+40%）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：骑兵封建起生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -955,27 +963,27 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>马厩单位城堡/帝王费用-15/20%</t>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -985,7 +993,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>斥候系费用-15%</t>
+          <t>血统/篷车效果+50%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -995,17 +1003,17 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：血统/篷车效果+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1015,27 +1023,27 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%；明光铠（骑兵单位近战护甲+4）；骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1045,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵；萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1055,17 +1063,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 4/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：兵营/靶场/马厩可用招募训令</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1075,27 +1083,27 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 0 / 弱 2）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：骑兵封建/城堡/帝王移速+5/10/15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1105,22 +1113,292 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>封建时代起</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>死士（骑兵攻击+5）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：死士（骑兵攻击+5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>城堡时代起</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代起</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：马厩单位城堡/帝王费用-15/20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：马厩科技研究+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>古典时代起</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 8/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>封建起骑乘/火枪骑攻速+25%</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>封建时代起</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代起</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>黑暗时代起</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 2/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1132,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1170,7 +1448,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1182,223 +1460,223 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
+          <t>骑兵对掷矛手攻+2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>象兵额外受伤-25%且抗招降</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>减少受到的伤害，正面更耐打</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>孟加拉</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>派（战车/象兵攻速+20%）</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>高棉</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>象兵移速+10%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>机动性提升</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>高棉</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>獠牙剑（象兵攻击+3）</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>高棉</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>额外一次的投掷/发射，等于直接翻倍输出</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>达罗毗荼</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>达罗毗荼</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>医疗部队（象兵每分钟恢复30生命）</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>象兵近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1408,7 +1686,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击无视护甲，克制重甲目标</t>
         </is>
       </c>
     </row>
@@ -1420,22 +1698,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>宝伞（象兵生命+100）</t>
+          <t>象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1725,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>曼尼普尔马（骑兵对远程攻+4）</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1462,7 +1740,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -1474,54 +1752,729 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>瞿折罗</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>马镫（骑兵攻速+33%）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>骑兵封建起生命+20%</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>骑士精神（马厩工作速度+40%）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>契丹</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>战斗中持续回血：攻速越快回得越多，是唯一的骑兵续航引擎，缠斗越久优势越大</t>
         </is>
       </c>
     </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>血统/篷车效果+50%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>直接强化象兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>骑兵对攻城武器的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>兵营/靶场/马厩可用招募训令</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>步兵护甲升级适用于骑兵</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>死士（骑兵攻击+5）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>马厩科技研究+50%</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>直接强化象兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>萨加里斯斧（骑兵无法格挡伤害+2）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>封建起骑乘/火枪骑攻速+25%</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1578,17 +2531,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>刹帝利（军事单位食物-25%）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -1598,24 +2551,24 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>马厩单位城堡/帝王费用-15/20%</t>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1632,12 +2585,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>斥候系费用-15%</t>
+          <t>靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1647,7 +2600,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -1659,125 +2612,125 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>马厩单位城堡/帝王费用-15/20%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>所有单位黄金费用-20%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>血统/斥候食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>贵族特权（骑士黄金费用-60%）</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1799,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1899,12 +2852,12 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1914,7 +2867,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -2053,12 +3006,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>防御和海军文明</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2068,19 +3021,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>防御和海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2090,19 +3043,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和攻城武器文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2112,19 +3065,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>防御和骑兵文明</t>
+          <t>骑兵和僧侣文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2134,19 +3087,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2156,19 +3109,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>骑兵与反制单位文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2178,19 +3131,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2200,19 +3153,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>弓兵文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2222,19 +3175,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>骑射手文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2244,19 +3197,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>弓兵文明</t>
+          <t>弓兵与僧侣文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2266,19 +3219,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>骑射手文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2288,19 +3241,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2310,19 +3263,19 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>骆驼和海军文明</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2332,19 +3285,19 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2354,19 +3307,19 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2376,19 +3329,19 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>骆驼和海军文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2398,19 +3351,19 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>火药文明</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2420,19 +3373,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2442,19 +3395,19 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2464,19 +3417,19 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2486,19 +3439,19 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>骑兵和海军文明</t>
+          <t>步兵和骑兵文明</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2508,19 +3461,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>骑兵文明</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2530,19 +3483,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2552,19 +3505,19 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2574,19 +3527,19 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>骆驼和火药文明</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2596,19 +3549,19 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2618,19 +3571,19 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>骑兵文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2640,19 +3593,19 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2662,19 +3615,19 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2684,210 +3637,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>骆驼和火药文明</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>步兵文明</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>步弓手和火药文明</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>阿契美尼德</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>弓兵和骑兵文明</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「造船厂工作速度+15%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>步兵和骑兵文明</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「高地受伤-10%」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>弓兵和象兵文明</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>步兵文明</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「精锐掷矛手升级免费」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>斯巴达</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>步兵文明</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强象兵</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D49"/>
+  <autoFilter ref="A1:D40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2899,7 +3654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2952,12 +3707,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+          <t>骑兵对掷矛手攻+2；象兵额外受伤-25%且抗招降</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 13/16。缺：重弩战象、精锐重弩战象、宝伞</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 13/16。缺：重弩战象、精锐重弩战象、宝伞</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3762,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：精锐战斗象、重弩战象、精锐重弩战象、血统、骑兵板甲</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 10/16。缺：精锐战斗象、重弩战象、精锐重弩战象、血统、骑兵板甲</t>
         </is>
       </c>
     </row>
@@ -3027,12 +3782,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>象兵近战护甲+1/远程护甲+1；曼尼普尔马（骑兵对远程攻+4）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 9/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 9/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3832,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>骑兵封建/城堡/帝王额外伤害+20/30/40%；边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；象兵科技树 10/16。缺：战斗象、精锐战斗象、重弩战象、精锐重弩战象、高炉</t>
+          <t>原生条目 4 条（强 3）；象兵科技树 10/16。缺：战斗象、精锐战斗象、重弩战象、精锐重弩战象、高炉</t>
         </is>
       </c>
     </row>
@@ -3092,22 +3847,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>7/16</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>马镫（骑兵攻速+33%）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；象兵科技树 5/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 1 条（强 1）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3872,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3127,12 +3882,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>骑兵封建起生命+20%；王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1）；象兵科技树 6/16。缺：骑象弓兵、精锐骑象弓兵、装甲象、攻城象、重弩战象</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 6/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -3142,22 +3897,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>马厩单位城堡/帝王费用-15/20%</t>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%；斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 2 条（强 2）；象兵科技树 5/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3922,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3177,12 +3932,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>斥候系费用-15%</t>
+          <t>血统/篷车效果+50%</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 1 条（强 1）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -3192,22 +3947,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%；明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 6/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3972,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>4/16</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 4/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3997,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3252,12 +4007,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0）；象兵科技树 6/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 3 条（强 3）；象兵科技树 6/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
@@ -3267,27 +4022,52 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>7/16</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；象兵科技树 2/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+          <t>原生条目 2 条（强 2）；象兵科技树 7/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>死士（骑兵攻击+5）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>原生条目 1 条（强 1）；象兵科技树 6/16。缺：战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵、装甲象</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3351,7 +4131,7 @@
           <t>孟加拉</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3361,14 +4141,14 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）；骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：象兵额外受伤-25%且抗招降</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 13/16；缺 重弩战象、精锐重弩战象、宝伞；最直接一条：骑兵对掷矛手攻+2</t>
         </is>
       </c>
     </row>
@@ -3381,7 +4161,7 @@
           <t>高棉</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3391,7 +4171,7 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>象兵移速+10%；獠牙剑（象兵攻击+3）；双箭弩（重弩战象/蝎式弩可多发一枚弩箭）</t>
         </is>
@@ -3411,7 +4191,7 @@
           <t>达罗毗荼</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -3421,14 +4201,14 @@
           <t>免费位</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>掷矛手/骑象弓兵攻速+25%；医疗部队（象兵每分钟恢复30生命）</t>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>掷矛手/骑象弓兵攻速+25%；医疗部队（象兵每分钟恢复30生命）；乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 10/16；缺 精锐战斗象、重弩战象、精锐重弩战象、血统；最直接一条：掷矛手/骑象弓兵攻速+25%</t>
         </is>
       </c>
     </row>
@@ -3451,14 +4231,14 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）；曼尼普尔马（骑兵对远程攻+4）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 9/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -3481,7 +4261,7 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>宝伞（象兵生命+100）</t>
         </is>
@@ -3511,14 +4291,14 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>阶段1·本体强化；原生条目 7 条（强 3 / 弱 1）；象兵科技树 10/16；缺 战斗象、精锐战斗象、重弩战象、精锐重弩战象；最直接一条：骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
     </row>
@@ -3528,7 +4308,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>保加利亚</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3541,14 +4321,14 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>马镫（骑兵攻速+33%）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：斡鲁朵骑兵（骑兵战斗中回血）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：马镫（骑兵攻速+33%）</t>
         </is>
       </c>
     </row>
@@ -3558,7 +4338,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3571,24 +4351,24 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>骑兵封建起生命+20%；骑士精神（马厩工作速度+40%）</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：骑兵封建起生命+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3601,24 +4381,24 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>马厩单位城堡/帝王费用-15/20%</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）；掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 5/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3631,24 +4411,24 @@
           <t>2000 金</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>斥候系费用-15%</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>血统/篷车效果+50%</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：血统/篷车效果+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -3663,22 +4443,22 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>所有单位黄金费用-20%</t>
+          <t>黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%；明光铠（骑兵单位近战护甲+4）；骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3693,22 +4473,22 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵；萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 4/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：兵营/靶场/马厩可用招募训令</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -3723,22 +4503,22 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>血统/斥候食物费用-50%；贵族特权（骑士黄金费用-60%）</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 2 条（强 0 / 弱 2）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 3 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：骑兵封建/城堡/帝王移速+5/10/15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3753,102 +4533,102 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 2/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>死士（骑兵攻击+5）</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始黄金+50」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：死士（骑兵攻击+5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：马厩单位城堡/帝王费用-15/20%</t>
         </is>
       </c>
     </row>
@@ -3858,57 +4638,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>保加利亚</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「民兵系升级免费」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：马厩科技研究+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；象兵科技树 8/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵；最直接一条：附近无敌人时马厩单位每分钟回25生命（古典起）</t>
         </is>
       </c>
     </row>
@@ -3918,57 +4698,57 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>女真</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>封建起骑乘/火枪骑攻速+25%</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；象兵科技树 6/16；缺 骑象弓兵、精锐骑象弓兵、装甲象、攻城象；最直接一条：象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
     </row>
@@ -3978,27 +4758,27 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 7/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -4008,27 +4788,27 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强象兵</t>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；象兵科技树 2/16；缺 战斗象、精锐战斗象、骑象弓兵、精锐骑象弓兵</t>
         </is>
       </c>
     </row>
@@ -4038,10 +4818,10 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+          <t>阿兹特克</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4058,7 +4838,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -4068,10 +4848,10 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4088,7 +4868,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工速度+15%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代获得黄金+100、食物+100」）</t>
         </is>
       </c>
     </row>
@@ -4098,10 +4878,10 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4118,7 +4898,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑黑暗/封建/城堡/帝王生命+10/20/30/40%」）</t>
         </is>
       </c>
     </row>
@@ -4128,10 +4908,10 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4148,7 +4928,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「大庄园替代磨坊」）</t>
         </is>
       </c>
     </row>
@@ -4158,10 +4938,10 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4178,7 +4958,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>防御和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局有骡车」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始木材/食物+50」）</t>
         </is>
       </c>
     </row>
@@ -4188,10 +4968,10 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
+          <t>波希米亚</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4208,7 +4988,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -4218,10 +4998,10 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4238,7 +5018,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「封建可额外建一座TC」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可提前一个时代经济升级且食物-40%」）</t>
         </is>
       </c>
     </row>
@@ -4248,10 +5028,10 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
+          <t>不列颠</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4268,7 +5048,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -4278,10 +5058,10 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4298,7 +5078,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牲畜持续时间+50%」）</t>
         </is>
       </c>
     </row>
@@ -4308,10 +5088,10 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
+          <t>丹麦人</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4328,7 +5108,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑木材-15%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -4338,10 +5118,10 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
+          <t>高丽</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4358,7 +5138,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -4368,10 +5148,10 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
+          <t>哥特</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4388,7 +5168,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -4398,10 +5178,10 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
+          <t>凯尔特</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4418,7 +5198,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4428,10 +5208,10 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4448,7 +5228,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>骑兵和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每座TC食物+100」）</t>
         </is>
       </c>
     </row>
@@ -4458,10 +5238,10 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4478,7 +5258,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民收集/建造/修理速度+5%」）</t>
         </is>
       </c>
     </row>
@@ -4488,10 +5268,10 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4508,7 +5288,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>骑兵与反制单位文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采果工存食+25%」）</t>
         </is>
       </c>
     </row>
@@ -4518,10 +5298,10 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4538,7 +5318,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民一击杀狼」）</t>
         </is>
       </c>
     </row>
@@ -4548,10 +5328,10 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+          <t>玛雅</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4568,7 +5348,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -4578,10 +5358,10 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4598,7 +5378,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>骑射手文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「猎人速度+40%」）</t>
         </is>
       </c>
     </row>
@@ -4608,10 +5388,10 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
+          <t>穆伊斯卡</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4628,7 +5408,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农田费用-40%」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -4638,10 +5418,10 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4658,7 +5438,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
@@ -4668,10 +5448,10 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
+          <t>撒克逊人</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4688,7 +5468,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>骑兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「牧羊/捕鱼/狩猎也产黄金」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
@@ -4698,10 +5478,10 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4718,7 +5498,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
+          <t>骆驼和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「市场贸易税仅5%」）</t>
         </is>
       </c>
     </row>
@@ -4728,10 +5508,10 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
+          <t>蜀</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4748,7 +5528,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「每研究一次经济升级免费获一村民」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
@@ -4758,10 +5538,10 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
+          <t>斯拉夫</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4778,7 +5558,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -4788,10 +5568,10 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
+          <t>图皮</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4808,7 +5588,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
@@ -4818,10 +5598,10 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4838,7 +5618,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
+          <t>火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「金矿工速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -4848,10 +5628,10 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4868,7 +5648,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
@@ -4878,10 +5658,10 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4898,7 +5678,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「军事建筑/码头建成后食物+55」）</t>
         </is>
       </c>
     </row>
@@ -4908,10 +5688,10 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4928,7 +5708,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
@@ -4938,10 +5718,10 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4958,7 +5738,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
+          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始石料+100」）</t>
         </is>
       </c>
     </row>
@@ -4968,10 +5748,10 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4988,7 +5768,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「不需要房屋，但初始木材-100」）</t>
         </is>
       </c>
     </row>
@@ -4998,10 +5778,10 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
+          <t>亚美尼亚</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5018,7 +5798,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5808,10 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5048,7 +5828,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>弓兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「造船厂工作速度+15%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
@@ -5058,10 +5838,10 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5078,7 +5858,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>步兵和骑兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「高地受伤-10%」）</t>
+          <t>骆驼和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「村民黑暗/封建/城堡/帝王费用-8/13/18/23%」）</t>
         </is>
       </c>
     </row>
@@ -5088,10 +5868,10 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5108,7 +5888,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>弓兵和象兵文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「采石村民缓慢获食」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于象兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5901,7 @@
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5151,7 +5931,7 @@
           <t>斯巴达</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5181,7 +5961,7 @@
           <t>雅典</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -5223,276 +6003,276 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>《帝国时代2 决定版》象兵流最优研究顺序</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>By RemonBo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="12" t="inlineStr"/>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr"/>
     </row>
     <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>口径</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>62 个按钮 = 各文明的全部特性（主要功能 + 独特科技 + 团队加成），不含独特单位。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="11" t="inlineStr"/>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr"/>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>团队加成按「对自己生效」计算，不因原本是全队加成而降权。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="11" t="inlineStr"/>
-      <c r="B5" s="11" t="inlineStr"/>
+      <c r="A5" s="12" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>决定性前提 1</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>象兵出自马厩（城堡时代解锁），造价极高（食物 + 黄金），是典型的「一波定胜负」兵种。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>决定性前提 2</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>象兵生命极高但移速慢、怕长矛兵系与僧侣招降；象轿/宝伞/獠牙剑类专有科技决定其上限。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>决定性前提 3</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>全表共 10 个文明拥有象兵系单位（孟加拉/高棉/达罗毗荼/缅甸/越南/马来/瞿折罗/波斯/印度斯坦/普鲁人），但只有前 7 家带象兵专属加成——主选文明必须先解决「能不能出象」，再谈按钮加成。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>决定性前提 4</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>契丹的「斡鲁朵骑兵」对战斗象/装甲象/战象生效（它们同属骑兵类），对骑象弓兵不生效——但契丹自己造不出象兵，它出现在本表是作为「按钮选项」：底座文明能出象时，再买契丹按钮即可让象兵战斗中回血。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="11" t="inlineStr"/>
-      <c r="B10" s="11" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>模组专属：按钮机制</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="49" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>模组专属：契丹「斡鲁朵骑兵」对象兵有效</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>该效果的真实实现是给 dat class 12（骑兵）与 class 47（斥候）统一加「战斗中回血」，再逐个剔除名单外的单位。战斗象、装甲象、老式战象（以及印度的 ELEITIS）类别都是 12，因此都能战斗中回血；骑象弓兵（class 36）不生效，重弩战象被官方显式排除。所以「象兵流 + 契丹按钮」是可行的组合，但别指望骑象弓兵也回血。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>模组专属：无象兵 SSR</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>除上述外，模组文本（v21）中没有针对象兵的独立按钮或 SSR 互斥项。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>排序口径</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>① 阶段 1 · 本体强化</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>直接加强象兵本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>② 阶段 2 · 减费用</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>降低该兵种及同系兵种（骑兵系／马厩单位（象兵属骑兵类））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>③ 阶段 3 · 资源效率</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="11" t="inlineStr"/>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr"/>
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与象兵流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
-      <c r="B20" s="11" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr"/>
+      <c r="B20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>未验证项</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>★ 最重要的一条：别买重复</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="11" t="inlineStr"/>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr"/>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>数据来源</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="11" t="inlineStr"/>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>
